--- a/docs/files/2026-09-28/상담행정공고_2026-09-28.xlsx
+++ b/docs/files/2026-09-28/상담행정공고_2026-09-28.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -815,136 +815,128 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 행정</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr"/>
+          <t>상담 · 청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>국가아동권리보장원</t>
+          <t>도봉구청소년상담복지센터</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
+          <t>2026년도봉구청소년상담복지센터팀원(청소년안전망) 채용 재공고</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>정규직,비정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울,경기</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,대졸(4년)</t>
-        </is>
-      </c>
+          <t>서울특별시 도봉구</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
-        </is>
-      </c>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068986</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
+          <t>청소년 · 복지 · 행정</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>건설근로자공제회</t>
+          <t>국가아동권리보장원</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
+          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
+          <t>정규직,비정규직</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
+          <t>서울,경기</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>학력무관,고졸</t>
+          <t>학력무관,대졸(4년)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
+          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
+          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -954,70 +946,70 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://cw.careerlink.kr</t>
+          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>행정 · 교육</t>
+          <t>상담 · 행정</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교</t>
+          <t>건설근로자공제회</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
+          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>비정규직</t>
+          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>학력무관</t>
+          <t>학력무관,고졸</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
+          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1027,35 +1019,35 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
+          <t>https://cw.careerlink.kr</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>관악청소년자립지원관(이용형,들꽃)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>관악청소년자립지원관(이용형,들꽃) 2026년 4차 자립지원요원(계약직) 채용 공고</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시 관악구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1066,17 +1058,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1088,117 +1080,129 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069235</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>행정 · 교육</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>이음</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>임상심리치료전문인력 채용</t>
+          <t>한국기술교육대학교 직업능력심사평가원 대체인력 채용(5차) 공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>비정규직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>D-9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>학력·경력·연령·성별 등에 따른 일체의 제한 없음.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+          <t>https://www.koreatech.ac.kr/notice/view.es?mid=a10604040000&amp;board_id=150&amp;post_seq=847&amp;prefix_id=</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>서울특별시 양천구</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1210,35 +1214,35 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1249,17 +1253,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-19</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1271,12 +1275,195 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>이음</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>임상심리치료전문인력 채용</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>경기도 수원시</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O12"/>
+  <autoFilter ref="A1:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
